--- a/data/trans_dic/IP11C$medico-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,41</t>
+          <t>0,0; 71,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,46</t>
+          <t>0,0; 33,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,53</t>
+          <t>0,0; 60,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 28,94</t>
+          <t>2,82; 29,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>0,0; 11,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,41</t>
+          <t>0,0; 47,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 26,45</t>
+          <t>6,13; 26,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 24,07</t>
+          <t>6,17; 24,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 21,72</t>
+          <t>2,2; 20,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,95</t>
+          <t>0,0; 26,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 22,26</t>
+          <t>7,86; 23,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,93</t>
+          <t>4,08; 14,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,67</t>
+          <t>1,45; 13,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 24,85</t>
+          <t>1,57; 23,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,34</t>
+          <t>0,0; 44,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,95</t>
+          <t>0,0; 41,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,8</t>
+          <t>0,0; 17,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,83</t>
+          <t>0,0; 39,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,23</t>
+          <t>0,0; 65,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,93</t>
+          <t>0,0; 20,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 19,65</t>
+          <t>1,69; 19,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,75</t>
+          <t>0,0; 31,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,02</t>
+          <t>0,0; 45,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 21,0</t>
+          <t>3,65; 20,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,3</t>
+          <t>1,18; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,83</t>
+          <t>0,0; 30,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 24,22</t>
+          <t>7,41; 24,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,17</t>
+          <t>5,37; 16,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,83</t>
+          <t>1,75; 16,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 31,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 19,83</t>
+          <t>7,75; 19,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,31</t>
+          <t>4,35; 12,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,88</t>
+          <t>1,51; 11,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 24,39</t>
+          <t>3,24; 23,58</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2946</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2123</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4188</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4213</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3438</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2325</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>594; 6130</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4482</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5267</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2265; 9686</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2772; 10874</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>691; 6323</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3876</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4557; 13894</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3382; 12411</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>693; 6261</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>405; 6037</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4328</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2826</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2782</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2655</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5233</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3418</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>432; 4968</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3540</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5959</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7111</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>610; 6728</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5252</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3448; 11613</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3937; 12053</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>715; 6852</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 7475</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6338; 15907</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5443; 15581</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>967; 7594</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1334; 9712</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$medico-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Estudios-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,62</t>
+          <t>0,0; 70,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,28</t>
+          <t>0,0; 23,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,59</t>
+          <t>0,0; 61,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,67</t>
+          <t>0,0; 19,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 29,13</t>
+          <t>3,4; 27,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 11,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,8</t>
+          <t>0,0; 42,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 26,23</t>
+          <t>7,62; 27,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 24,22</t>
+          <t>5,96; 24,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 20,14</t>
+          <t>2,21; 19,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,28</t>
+          <t>0,0; 32,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 23,97</t>
+          <t>8,17; 23,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 14,98</t>
+          <t>4,24; 14,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,07</t>
+          <t>1,43; 12,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 23,43</t>
+          <t>1,65; 24,43</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,58</t>
+          <t>0,0; 40,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,78</t>
+          <t>0,0; 49,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,5</t>
+          <t>0,0; 17,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,01</t>
+          <t>0,0; 39,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,93</t>
+          <t>0,0; 60,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,21</t>
+          <t>0,0; 22,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 19,4</t>
+          <t>1,7; 19,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,55</t>
+          <t>0,0; 23,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,88</t>
+          <t>0,0; 45,64</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 20,14</t>
+          <t>3,64; 21,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,01</t>
+          <t>1,17; 11,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,62</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 24,96</t>
+          <t>7,67; 25,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 16,43</t>
+          <t>5,31; 16,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,83</t>
+          <t>1,82; 17,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 29,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 19,44</t>
+          <t>7,71; 20,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,46</t>
+          <t>4,53; 12,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,85</t>
+          <t>1,53; 10,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 23,58</t>
+          <t>2,53; 24,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2946</t>
+          <t>0; 2918</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4188</t>
+          <t>0; 2917</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4213</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 3217</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>594; 6130</t>
+          <t>716; 5789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4482</t>
+          <t>0; 4510</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1727,47 +1727,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5267</t>
+          <t>0; 4641</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2265; 9686</t>
+          <t>2814; 10215</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2772; 10874</t>
+          <t>2674; 10810</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>691; 6323</t>
+          <t>694; 6112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 4790</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4557; 13894</t>
+          <t>4733; 13688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3382; 12411</t>
+          <t>3510; 12242</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>693; 6261</t>
+          <t>687; 6175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>405; 6037</t>
+          <t>425; 6293</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4328</t>
+          <t>0; 3966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1940,42 +1940,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2826</t>
+          <t>0; 3367</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2782</t>
+          <t>0; 2795</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2655</t>
+          <t>0; 2711</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5233</t>
+          <t>0; 4799</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3418</t>
+          <t>0; 3723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>432; 4968</t>
+          <t>435; 5092</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 2631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5959</t>
+          <t>0; 5927</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1290; 7111</t>
+          <t>1284; 7505</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>610; 6728</t>
+          <t>607; 6107</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2143,47 +2143,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3448; 11613</t>
+          <t>3566; 11877</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3937; 12053</t>
+          <t>3899; 12435</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>715; 6852</t>
+          <t>741; 6975</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7475</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6338; 15907</t>
+          <t>6305; 16421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5443; 15581</t>
+          <t>5667; 16233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>967; 7594</t>
+          <t>980; 6928</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1334; 9712</t>
+          <t>1042; 10170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$medico-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,32 +649,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23,67%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,59%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,93</t>
+          <t>0,0; 74,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,79</t>
+          <t>0,0; 71,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,04</t>
+          <t>0,0; 53,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,34</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>12,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 27,51</t>
+          <t>7,1; 26,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,88</t>
+          <t>6,17; 24,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,2; 21,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,12</t>
+          <t>0,0; 30,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 27,67</t>
+          <t>3,33; 28,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 24,08</t>
+          <t>0,0; 12,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 19,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,49</t>
+          <t>0,0; 41,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 23,61</t>
+          <t>7,23; 22,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,78</t>
+          <t>4,09; 14,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,89</t>
+          <t>1,46; 12,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 24,43</t>
+          <t>1,36; 25,37</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>3,98%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 51,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,85</t>
+          <t>0,0; 17,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 39,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 68,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 40,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,02</t>
+          <t>0,0; 20,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 19,89</t>
+          <t>1,7; 19,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,45</t>
+          <t>0,0; 28,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,64</t>
+          <t>0,0; 52,61</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 21,26</t>
+          <t>7,39; 24,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,81</t>
+          <t>4,76; 17,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,81; 17,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 25,53</t>
+          <t>3,73; 21,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 16,95</t>
+          <t>1,18; 11,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,46</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,07</t>
+          <t>7,69; 19,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,98</t>
+          <t>4,57; 12,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 10,81</t>
+          <t>1,15; 10,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,69</t>
+          <t>3,1; 25,23</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1436,32 +1436,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2918</t>
+          <t>0; 2123</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2123</t>
+          <t>0; 2938</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2917</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>0; 3722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 3432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2616</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2249</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>716; 5789</t>
+          <t>2623; 9767</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4510</t>
+          <t>2771; 10807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>689; 6817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 4237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2814; 10215</t>
+          <t>702; 6090</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2674; 10810</t>
+          <t>0; 4584</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>694; 6112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 4522</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4733; 13688</t>
+          <t>4191; 12902</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3510; 12242</t>
+          <t>3386; 12370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>687; 6175</t>
+          <t>697; 6070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>425; 6293</t>
+          <t>335; 6271</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,49 +1852,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>1817</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1526</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3514</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3966</t>
+          <t>0; 2830</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5046</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3367</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2795</t>
+          <t>0; 3916</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2711</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4799</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3723</t>
+          <t>0; 3538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>435; 5092</t>
+          <t>435; 5033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2631</t>
+          <t>0; 3225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5927</t>
+          <t>0; 6549</t>
         </is>
       </c>
     </row>
@@ -1992,37 +1992,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2060,62 +2060,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>3040</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3774</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1284; 7505</t>
+          <t>3440; 11266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>607; 6107</t>
+          <t>3493; 12598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>739; 7259</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5219</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3566; 11877</t>
+          <t>1317; 7413</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3899; 12435</t>
+          <t>611; 5845</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>741; 6975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 4756</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6305; 16421</t>
+          <t>6291; 16223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5667; 16233</t>
+          <t>5717; 15402</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>980; 6928</t>
+          <t>737; 6970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1042; 10170</t>
+          <t>1223; 9950</t>
         </is>
       </c>
     </row>
